--- a/request_forms/020_multi_store_account_merge_request_form--request_forms.xlsx
+++ b/request_forms/020_multi_store_account_merge_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'store_a',_'label':_'store_a'}</t>
+          <t>store_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'store_a', 'label': 'Store A'}</t>
+          <t>Store A</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'store_b',_'label':_'store_b'}</t>
+          <t>store_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'store_b', 'label': 'Store B'}</t>
+          <t>Store B</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'store_c',_'label':_'store_c'}</t>
+          <t>store_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'store_c', 'label': 'Store C'}</t>
+          <t>Store C</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'store_d',_'label':_'store_d'}</t>
+          <t>store_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'store_d', 'label': 'Store D'}</t>
+          <t>Store D</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'store_e',_'label':_'store_e'}</t>
+          <t>store_e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'store_e', 'label': 'Store E'}</t>
+          <t>Store E</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'store_f',_'label':_'store_f'}</t>
+          <t>store_f</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'store_f', 'label': 'Store F'}</t>
+          <t>Store F</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'store_g',_'label':_'store_g'}</t>
+          <t>store_g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'store_g', 'label': 'Store G'}</t>
+          <t>Store G</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'store_h',_'label':_'store_h'}</t>
+          <t>store_h</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'store_h', 'label': 'Store H'}</t>
+          <t>Store H</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'store_i',_'label':_'store_i'}</t>
+          <t>store_i</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'store_i', 'label': 'Store I'}</t>
+          <t>Store I</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'store_j',_'label':_'store_j'}</t>
+          <t>store_j</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'store_j', 'label': 'Store J'}</t>
+          <t>Store J</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'store_k',_'label':_'store_k'}</t>
+          <t>store_k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'store_k', 'label': 'Store K'}</t>
+          <t>Store K</t>
         </is>
       </c>
     </row>
